--- a/서버정보/20260921_리소스배포_운영.xlsx
+++ b/서버정보/20260921_리소스배포_운영.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zenithn\PowerShell - 리소스 배포\서버정보\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1D2E847-B6E7-41E3-AFC3-CDEDBCE56F89}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E83BB4B2-7D18-4D40-9DE3-5E62B2329385}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="VNET" sheetId="4" r:id="rId1"/>
@@ -1661,7 +1661,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8181" uniqueCount="1171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8173" uniqueCount="1181">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -5930,10 +5930,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>hazr-p-dis-rg</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>hazr-p-dis-gaoweb01</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -5983,6 +5979,50 @@
   </si>
   <si>
     <t>10.158.128.50</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-p-clv-rg</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-p-clv-web01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-p-clv-web02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-p-clv-ap01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-p-clv-ap02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-p-clv-ssrap01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-p-clv-ssrap02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-p-clv-admweb01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-p-clv-admweb02</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-p-clv-admap01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hazr-p-clv-admap02</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -13855,7 +13895,7 @@
         <v>922</v>
       </c>
       <c r="E78" s="74" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="F78" s="74" t="str">
         <f t="shared" si="34"/>
@@ -13916,7 +13956,7 @@
         <v>922</v>
       </c>
       <c r="E79" s="82" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="F79" s="82" t="str">
         <f t="shared" si="34"/>
@@ -27788,21 +27828,22 @@
       <c r="AF147" s="95"/>
     </row>
     <row r="148" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A148" s="90"/>
       <c r="B148" s="95" t="s">
         <v>23</v>
       </c>
       <c r="C148" s="74" t="str" cm="1">
         <f t="array" ref="C148">UPPER(INDEX(_xlfn.TEXTSPLIT($F148, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D148" s="74" t="s">
-        <v>1116</v>
+        <v>1170</v>
       </c>
       <c r="E148" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F148" s="82" t="s">
-        <v>1117</v>
+        <v>1171</v>
       </c>
       <c r="G148" s="74" t="s">
         <v>1143</v>
@@ -27830,7 +27871,7 @@
       </c>
       <c r="O148" s="117" t="str">
         <f t="shared" ref="O148:O157" si="18">SUBSTITUTE(F148,"hazr-","")&amp;"-osdisk"</f>
-        <v>p-dis-clvweb01-osdisk</v>
+        <v>p-clv-web01-osdisk</v>
       </c>
       <c r="P148" s="112">
         <v>64</v>
@@ -27843,7 +27884,7 @@
       <c r="T148" s="74"/>
       <c r="U148" s="74" t="str">
         <f t="shared" ref="U148:U157" si="19">SUBSTITUTE(F148,"hazr-","")&amp;"-nic"</f>
-        <v>p-dis-clvweb01-nic</v>
+        <v>p-clv-web01-nic</v>
       </c>
       <c r="V148" s="95" t="b">
         <v>1</v>
@@ -27876,21 +27917,22 @@
       <c r="AF148" s="74"/>
     </row>
     <row r="149" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A149" s="90"/>
       <c r="B149" s="95" t="s">
         <v>23</v>
       </c>
       <c r="C149" s="74" t="str" cm="1">
         <f t="array" ref="C149">UPPER(INDEX(_xlfn.TEXTSPLIT($F149, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D149" s="74" t="s">
-        <v>1116</v>
+        <v>1170</v>
       </c>
       <c r="E149" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F149" s="74" t="s">
-        <v>1118</v>
+        <v>1172</v>
       </c>
       <c r="G149" s="74" t="s">
         <v>1144</v>
@@ -27918,7 +27960,7 @@
       </c>
       <c r="O149" s="117" t="str">
         <f t="shared" si="18"/>
-        <v>p-dis-clvweb02-osdisk</v>
+        <v>p-clv-web02-osdisk</v>
       </c>
       <c r="P149" s="112">
         <v>64</v>
@@ -27931,7 +27973,7 @@
       <c r="T149" s="74"/>
       <c r="U149" s="74" t="str">
         <f t="shared" si="19"/>
-        <v>p-dis-clvweb02-nic</v>
+        <v>p-clv-web02-nic</v>
       </c>
       <c r="V149" s="95" t="b">
         <v>1</v>
@@ -27964,21 +28006,22 @@
       <c r="AF149" s="74"/>
     </row>
     <row r="150" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A150" s="90"/>
       <c r="B150" s="95" t="s">
         <v>23</v>
       </c>
       <c r="C150" s="74" t="str" cm="1">
         <f t="array" ref="C150">UPPER(INDEX(_xlfn.TEXTSPLIT($F150, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D150" s="74" t="s">
-        <v>1116</v>
+        <v>1170</v>
       </c>
       <c r="E150" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F150" s="82" t="s">
-        <v>1119</v>
+        <v>1173</v>
       </c>
       <c r="G150" s="74" t="s">
         <v>1145</v>
@@ -28006,7 +28049,7 @@
       </c>
       <c r="O150" s="117" t="str">
         <f t="shared" si="18"/>
-        <v>p-dis-clvap01-osdisk</v>
+        <v>p-clv-ap01-osdisk</v>
       </c>
       <c r="P150" s="112">
         <v>64</v>
@@ -28019,7 +28062,7 @@
       <c r="T150" s="74"/>
       <c r="U150" s="74" t="str">
         <f t="shared" si="19"/>
-        <v>p-dis-clvap01-nic</v>
+        <v>p-clv-ap01-nic</v>
       </c>
       <c r="V150" s="95" t="b">
         <v>1</v>
@@ -28052,21 +28095,22 @@
       <c r="AF150" s="74"/>
     </row>
     <row r="151" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A151" s="90"/>
       <c r="B151" s="95" t="s">
         <v>23</v>
       </c>
       <c r="C151" s="74" t="str" cm="1">
         <f t="array" ref="C151">UPPER(INDEX(_xlfn.TEXTSPLIT($F151, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D151" s="74" t="s">
-        <v>1116</v>
+        <v>1170</v>
       </c>
       <c r="E151" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F151" s="74" t="s">
-        <v>1120</v>
+        <v>1174</v>
       </c>
       <c r="G151" s="74" t="s">
         <v>1146</v>
@@ -28094,7 +28138,7 @@
       </c>
       <c r="O151" s="117" t="str">
         <f t="shared" si="18"/>
-        <v>p-dis-clvap02-osdisk</v>
+        <v>p-clv-ap02-osdisk</v>
       </c>
       <c r="P151" s="112">
         <v>64</v>
@@ -28107,7 +28151,7 @@
       <c r="T151" s="74"/>
       <c r="U151" s="74" t="str">
         <f t="shared" si="19"/>
-        <v>p-dis-clvap02-nic</v>
+        <v>p-clv-ap02-nic</v>
       </c>
       <c r="V151" s="95" t="b">
         <v>1</v>
@@ -28140,21 +28184,22 @@
       <c r="AF151" s="74"/>
     </row>
     <row r="152" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A152" s="90"/>
       <c r="B152" s="95" t="s">
         <v>23</v>
       </c>
       <c r="C152" s="74" t="str" cm="1">
         <f t="array" ref="C152">UPPER(INDEX(_xlfn.TEXTSPLIT($F152, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D152" s="74" t="s">
-        <v>1116</v>
+        <v>1170</v>
       </c>
       <c r="E152" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F152" s="82" t="s">
-        <v>1121</v>
+        <v>1175</v>
       </c>
       <c r="G152" s="74" t="s">
         <v>1147</v>
@@ -28182,7 +28227,7 @@
       </c>
       <c r="O152" s="117" t="str">
         <f t="shared" si="18"/>
-        <v>p-dis-clvssrap01-osdisk</v>
+        <v>p-clv-ssrap01-osdisk</v>
       </c>
       <c r="P152" s="112">
         <v>64</v>
@@ -28195,7 +28240,7 @@
       <c r="T152" s="74"/>
       <c r="U152" s="74" t="str">
         <f t="shared" si="19"/>
-        <v>p-dis-clvssrap01-nic</v>
+        <v>p-clv-ssrap01-nic</v>
       </c>
       <c r="V152" s="95" t="b">
         <v>1</v>
@@ -28228,21 +28273,22 @@
       <c r="AF152" s="74"/>
     </row>
     <row r="153" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A153" s="90"/>
       <c r="B153" s="95" t="s">
         <v>23</v>
       </c>
       <c r="C153" s="74" t="str" cm="1">
         <f t="array" ref="C153">UPPER(INDEX(_xlfn.TEXTSPLIT($F153, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D153" s="74" t="s">
-        <v>1116</v>
+        <v>1170</v>
       </c>
       <c r="E153" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F153" s="74" t="s">
-        <v>1122</v>
+        <v>1176</v>
       </c>
       <c r="G153" s="74" t="s">
         <v>1148</v>
@@ -28270,7 +28316,7 @@
       </c>
       <c r="O153" s="117" t="str">
         <f t="shared" si="18"/>
-        <v>p-dis-clvssrap02-osdisk</v>
+        <v>p-clv-ssrap02-osdisk</v>
       </c>
       <c r="P153" s="112">
         <v>64</v>
@@ -28283,7 +28329,7 @@
       <c r="T153" s="74"/>
       <c r="U153" s="74" t="str">
         <f t="shared" si="19"/>
-        <v>p-dis-clvssrap02-nic</v>
+        <v>p-clv-ssrap02-nic</v>
       </c>
       <c r="V153" s="95" t="b">
         <v>1</v>
@@ -28316,21 +28362,22 @@
       <c r="AF153" s="74"/>
     </row>
     <row r="154" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A154" s="90"/>
       <c r="B154" s="95" t="s">
         <v>23</v>
       </c>
       <c r="C154" s="74" t="str" cm="1">
         <f t="array" ref="C154">UPPER(INDEX(_xlfn.TEXTSPLIT($F154, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D154" s="74" t="s">
-        <v>1116</v>
+        <v>1170</v>
       </c>
       <c r="E154" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F154" s="82" t="s">
-        <v>1123</v>
+        <v>1177</v>
       </c>
       <c r="G154" s="74" t="s">
         <v>1149</v>
@@ -28358,7 +28405,7 @@
       </c>
       <c r="O154" s="117" t="str">
         <f t="shared" si="18"/>
-        <v>p-dis-clvadmweb01-osdisk</v>
+        <v>p-clv-admweb01-osdisk</v>
       </c>
       <c r="P154" s="112">
         <v>64</v>
@@ -28371,7 +28418,7 @@
       <c r="T154" s="74"/>
       <c r="U154" s="74" t="str">
         <f t="shared" si="19"/>
-        <v>p-dis-clvadmweb01-nic</v>
+        <v>p-clv-admweb01-nic</v>
       </c>
       <c r="V154" s="95" t="b">
         <v>1</v>
@@ -28404,21 +28451,22 @@
       <c r="AF154" s="74"/>
     </row>
     <row r="155" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A155" s="90"/>
       <c r="B155" s="95" t="s">
         <v>23</v>
       </c>
       <c r="C155" s="74" t="str" cm="1">
         <f t="array" ref="C155">UPPER(INDEX(_xlfn.TEXTSPLIT($F155, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D155" s="74" t="s">
-        <v>1116</v>
+        <v>1170</v>
       </c>
       <c r="E155" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F155" s="74" t="s">
-        <v>1125</v>
+        <v>1178</v>
       </c>
       <c r="G155" s="74" t="s">
         <v>1150</v>
@@ -28446,7 +28494,7 @@
       </c>
       <c r="O155" s="117" t="str">
         <f t="shared" si="18"/>
-        <v>p-dis-clvadmweb02-osdisk</v>
+        <v>p-clv-admweb02-osdisk</v>
       </c>
       <c r="P155" s="112">
         <v>64</v>
@@ -28459,7 +28507,7 @@
       <c r="T155" s="74"/>
       <c r="U155" s="74" t="str">
         <f t="shared" si="19"/>
-        <v>p-dis-clvadmweb02-nic</v>
+        <v>p-clv-admweb02-nic</v>
       </c>
       <c r="V155" s="95" t="b">
         <v>1</v>
@@ -28492,21 +28540,22 @@
       <c r="AF155" s="74"/>
     </row>
     <row r="156" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A156" s="90"/>
       <c r="B156" s="95" t="s">
         <v>23</v>
       </c>
       <c r="C156" s="74" t="str" cm="1">
         <f t="array" ref="C156">UPPER(INDEX(_xlfn.TEXTSPLIT($F156, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D156" s="74" t="s">
-        <v>1116</v>
+        <v>1170</v>
       </c>
       <c r="E156" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F156" s="82" t="s">
-        <v>1124</v>
+        <v>1179</v>
       </c>
       <c r="G156" s="74" t="s">
         <v>1151</v>
@@ -28534,7 +28583,7 @@
       </c>
       <c r="O156" s="117" t="str">
         <f t="shared" si="18"/>
-        <v>p-dis-clvadmap01-osdisk</v>
+        <v>p-clv-admap01-osdisk</v>
       </c>
       <c r="P156" s="112">
         <v>64</v>
@@ -28547,7 +28596,7 @@
       <c r="T156" s="74"/>
       <c r="U156" s="74" t="str">
         <f t="shared" si="19"/>
-        <v>p-dis-clvadmap01-nic</v>
+        <v>p-clv-admap01-nic</v>
       </c>
       <c r="V156" s="95" t="b">
         <v>1</v>
@@ -28580,21 +28629,22 @@
       <c r="AF156" s="74"/>
     </row>
     <row r="157" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A157" s="90"/>
       <c r="B157" s="95" t="s">
         <v>23</v>
       </c>
       <c r="C157" s="95" t="str" cm="1">
         <f t="array" ref="C157">UPPER(INDEX(_xlfn.TEXTSPLIT($F157, "-"), 3))</f>
-        <v>DIS</v>
+        <v>CLV</v>
       </c>
       <c r="D157" s="74" t="s">
-        <v>1116</v>
+        <v>1170</v>
       </c>
       <c r="E157" s="74" t="s">
         <v>24</v>
       </c>
       <c r="F157" s="95" t="s">
-        <v>1126</v>
+        <v>1180</v>
       </c>
       <c r="G157" s="95" t="s">
         <v>1152</v>
@@ -28622,7 +28672,7 @@
       </c>
       <c r="O157" s="120" t="str">
         <f t="shared" si="18"/>
-        <v>p-dis-clvadmap02-osdisk</v>
+        <v>p-clv-admap02-osdisk</v>
       </c>
       <c r="P157" s="112">
         <v>64</v>
@@ -28635,7 +28685,7 @@
       <c r="T157" s="95"/>
       <c r="U157" s="95" t="str">
         <f t="shared" si="19"/>
-        <v>p-dis-clvadmap02-nic</v>
+        <v>p-clv-admap02-nic</v>
       </c>
       <c r="V157" s="95" t="b">
         <v>1</v>
@@ -28668,27 +28718,24 @@
       <c r="AF157" s="95"/>
     </row>
     <row r="158" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A158" s="90"/>
       <c r="B158" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="C158" s="74" t="str" cm="1">
+      <c r="C158" s="74" t="e" cm="1">
         <f t="array" ref="C158">UPPER(INDEX(_xlfn.TEXTSPLIT($F158, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
-      <c r="D158" s="74" t="s">
-        <v>922</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D158" s="74"/>
       <c r="E158" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F158" s="74" t="s">
-        <v>1158</v>
-      </c>
+      <c r="F158" s="74"/>
       <c r="G158" s="74" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="H158" s="74" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="I158" s="74">
         <v>2</v>
@@ -28710,7 +28757,7 @@
       </c>
       <c r="O158" s="117" t="str">
         <f t="shared" ref="O158:O159" si="20">SUBSTITUTE(F158,"hazr-","")&amp;"-osdisk"</f>
-        <v>p-dis-gaoweb01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P158" s="112">
         <v>64</v>
@@ -28723,7 +28770,7 @@
       <c r="T158" s="74"/>
       <c r="U158" s="74" t="str">
         <f t="shared" ref="U158:U159" si="21">SUBSTITUTE(F158,"hazr-","")&amp;"-nic"</f>
-        <v>p-dis-gaoweb01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V158" s="95" t="b">
         <v>1</v>
@@ -28756,27 +28803,24 @@
       <c r="AF158" s="74"/>
     </row>
     <row r="159" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A159" s="90"/>
       <c r="B159" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="C159" s="74" t="str" cm="1">
+      <c r="C159" s="74" t="e" cm="1">
         <f t="array" ref="C159">UPPER(INDEX(_xlfn.TEXTSPLIT($F159, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
-      <c r="D159" s="74" t="s">
-        <v>922</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D159" s="74"/>
       <c r="E159" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F159" s="74" t="s">
-        <v>1159</v>
-      </c>
+      <c r="F159" s="74"/>
       <c r="G159" s="74" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="H159" s="74" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="I159" s="74">
         <v>2</v>
@@ -28798,7 +28842,7 @@
       </c>
       <c r="O159" s="117" t="str">
         <f t="shared" si="20"/>
-        <v>p-dis-gaoweb02-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P159" s="112">
         <v>64</v>
@@ -28811,7 +28855,7 @@
       <c r="T159" s="74"/>
       <c r="U159" s="74" t="str">
         <f t="shared" si="21"/>
-        <v>p-dis-gaoweb02-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V159" s="95" t="b">
         <v>1</v>
@@ -28844,27 +28888,24 @@
       <c r="AF159" s="74"/>
     </row>
     <row r="160" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A160" s="90"/>
       <c r="B160" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="C160" s="74" t="str" cm="1">
+      <c r="C160" s="74" t="e" cm="1">
         <f t="array" ref="C160">UPPER(INDEX(_xlfn.TEXTSPLIT($F160, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
-      <c r="D160" s="74" t="s">
-        <v>922</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D160" s="74"/>
       <c r="E160" s="74" t="s">
         <v>24</v>
       </c>
-      <c r="F160" s="74" t="s">
-        <v>1160</v>
-      </c>
+      <c r="F160" s="74"/>
       <c r="G160" s="74" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="H160" s="74" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="I160" s="74">
         <v>2</v>
@@ -28886,7 +28927,7 @@
       </c>
       <c r="O160" s="117" t="str">
         <f>SUBSTITUTE(F160,"hazr-","")&amp;"-osdisk"</f>
-        <v>p-dis-gaoap01-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P160" s="112">
         <v>64</v>
@@ -28899,7 +28940,7 @@
       <c r="T160" s="74"/>
       <c r="U160" s="74" t="str">
         <f>SUBSTITUTE(F160,"hazr-","")&amp;"-nic"</f>
-        <v>p-dis-gaoap01-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V160" s="95" t="b">
         <v>1</v>
@@ -28931,28 +28972,25 @@
       <c r="AE160" s="74"/>
       <c r="AF160" s="74"/>
     </row>
-    <row r="161" spans="2:32" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A161" s="90"/>
       <c r="B161" s="95" t="s">
         <v>23</v>
       </c>
-      <c r="C161" s="95" t="str" cm="1">
+      <c r="C161" s="95" t="e" cm="1">
         <f t="array" ref="C161">UPPER(INDEX(_xlfn.TEXTSPLIT($F161, "-"), 3))</f>
-        <v>DIS</v>
-      </c>
-      <c r="D161" s="95" t="s">
-        <v>1157</v>
-      </c>
+        <v>#VALUE!</v>
+      </c>
+      <c r="D161" s="95"/>
       <c r="E161" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="F161" s="95" t="s">
-        <v>1161</v>
-      </c>
+      <c r="F161" s="95"/>
       <c r="G161" s="95" t="s">
+        <v>1163</v>
+      </c>
+      <c r="H161" s="95" t="s">
         <v>1164</v>
-      </c>
-      <c r="H161" s="95" t="s">
-        <v>1165</v>
       </c>
       <c r="I161" s="95">
         <v>2</v>
@@ -28974,7 +29012,7 @@
       </c>
       <c r="O161" s="120" t="str">
         <f>SUBSTITUTE(F161,"hazr-","")&amp;"-osdisk"</f>
-        <v>p-dis-gaoap02-osdisk</v>
+        <v>-osdisk</v>
       </c>
       <c r="P161" s="112">
         <v>64</v>
@@ -28987,7 +29025,7 @@
       <c r="T161" s="95"/>
       <c r="U161" s="95" t="str">
         <f>SUBSTITUTE(F161,"hazr-","")&amp;"-nic"</f>
-        <v>p-dis-gaoap02-nic</v>
+        <v>-nic</v>
       </c>
       <c r="V161" s="95" t="b">
         <v>1</v>
@@ -37917,6 +37955,7 @@
       <c r="R166" s="80"/>
     </row>
     <row r="167" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A167" s="99"/>
       <c r="B167" s="78" t="s">
         <v>23</v>
       </c>
@@ -37931,7 +37970,7 @@
         <v>24</v>
       </c>
       <c r="F167" s="73" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="G167" s="73" t="str">
         <f t="shared" ref="G167:G170" si="7">SUBSTITUTE(F167,"hazr-","")&amp;"-disk01"</f>
@@ -37971,6 +38010,7 @@
       <c r="R167" s="78"/>
     </row>
     <row r="168" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A168" s="99"/>
       <c r="B168" s="80" t="s">
         <v>23</v>
       </c>
@@ -37985,7 +38025,7 @@
         <v>24</v>
       </c>
       <c r="F168" s="74" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="G168" s="74" t="str">
         <f t="shared" si="7"/>
@@ -38025,6 +38065,7 @@
       <c r="R168" s="80"/>
     </row>
     <row r="169" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A169" s="99"/>
       <c r="B169" s="78" t="s">
         <v>23</v>
       </c>
@@ -38039,7 +38080,7 @@
         <v>24</v>
       </c>
       <c r="F169" s="73" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="G169" s="73" t="str">
         <f t="shared" si="7"/>
@@ -38079,6 +38120,7 @@
       <c r="R169" s="78"/>
     </row>
     <row r="170" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A170" s="99"/>
       <c r="B170" s="80" t="s">
         <v>23</v>
       </c>
@@ -38093,7 +38135,7 @@
         <v>24</v>
       </c>
       <c r="F170" s="115" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="G170" s="74" t="str">
         <f t="shared" si="7"/>
@@ -45046,7 +45088,7 @@
         <v>346</v>
       </c>
       <c r="I176" s="73" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="J176" s="114" t="s">
         <v>922</v>
@@ -45085,7 +45127,7 @@
         <v>346</v>
       </c>
       <c r="I177" s="74" t="s">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="J177" s="115" t="s">
         <v>922</v>
@@ -45124,7 +45166,7 @@
         <v>340</v>
       </c>
       <c r="I178" s="73" t="s">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="J178" s="114" t="s">
         <v>922</v>
@@ -45163,7 +45205,7 @@
         <v>340</v>
       </c>
       <c r="I179" s="115" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
       <c r="J179" s="115" t="s">
         <v>922</v>
@@ -50340,7 +50382,7 @@
         <v>24</v>
       </c>
       <c r="F51" s="74" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="G51" s="74"/>
       <c r="H51" s="74" t="s">
@@ -50369,7 +50411,7 @@
         <v>108</v>
       </c>
       <c r="P51" s="74" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="Q51" s="74" t="str">
         <f t="shared" si="6"/>
@@ -50391,7 +50433,7 @@
         <v>24</v>
       </c>
       <c r="F52" s="82" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="G52" s="82"/>
       <c r="H52" s="82" t="s">
@@ -50420,7 +50462,7 @@
         <v>108</v>
       </c>
       <c r="P52" s="82" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="Q52" s="82" t="str">
         <f t="shared" si="6"/>
@@ -52986,7 +53028,7 @@
         <v>922</v>
       </c>
       <c r="E78" s="74" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="F78" s="74" t="str">
         <f t="shared" si="15"/>
@@ -53018,10 +53060,10 @@
         <v>922</v>
       </c>
       <c r="E79" s="82" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="F79" s="82" t="str">
-        <f>SUBSTITUTE(E79, "hazr-", "")&amp;"-pb"&amp;H79</f>
+        <f t="shared" ref="F79:F87" si="16">SUBSTITUTE(E79, "hazr-", "")&amp;"-pb"&amp;H79</f>
         <v>p-dis-gaopap-lb-pb8080</v>
       </c>
       <c r="G79" s="82" t="s">
@@ -53053,7 +53095,7 @@
         <v>1084</v>
       </c>
       <c r="F80" s="74" t="str">
-        <f>SUBSTITUTE(E80, "hazr-", "")&amp;"-pb"&amp;H80</f>
+        <f t="shared" si="16"/>
         <v>p-bdp-rlgcweb-lb-pb443</v>
       </c>
       <c r="G80" s="74" t="s">
@@ -53085,7 +53127,7 @@
         <v>1085</v>
       </c>
       <c r="F81" s="82" t="str">
-        <f>SUBSTITUTE(E81, "hazr-", "")&amp;"-pb"&amp;H81</f>
+        <f t="shared" si="16"/>
         <v>p-bdp-rlgcap-lb-pb9092</v>
       </c>
       <c r="G81" s="82" t="s">
@@ -53117,7 +53159,7 @@
         <v>1085</v>
       </c>
       <c r="F82" s="82" t="str">
-        <f>SUBSTITUTE(E82, "hazr-", "")&amp;"-pb"&amp;H82</f>
+        <f t="shared" si="16"/>
         <v>p-bdp-rlgcap-lb-pb9880</v>
       </c>
       <c r="G82" s="82" t="s">
@@ -53149,7 +53191,7 @@
         <v>1085</v>
       </c>
       <c r="F83" s="82" t="str">
-        <f>SUBSTITUTE(E83, "hazr-", "")&amp;"-pb"&amp;H83</f>
+        <f t="shared" si="16"/>
         <v>p-bdp-rlgcap-lb-pb29105</v>
       </c>
       <c r="G83" s="82" t="s">
@@ -53181,7 +53223,7 @@
         <v>1085</v>
       </c>
       <c r="F84" s="82" t="str">
-        <f>SUBSTITUTE(E84, "hazr-", "")&amp;"-pb"&amp;H84</f>
+        <f t="shared" si="16"/>
         <v>p-bdp-rlgcap-lb-pb29106</v>
       </c>
       <c r="G84" s="82" t="s">
@@ -53213,7 +53255,7 @@
         <v>1085</v>
       </c>
       <c r="F85" s="82" t="str">
-        <f>SUBSTITUTE(E85, "hazr-", "")&amp;"-pb"&amp;H85</f>
+        <f t="shared" si="16"/>
         <v>p-bdp-rlgcap-lb-pb29107</v>
       </c>
       <c r="G85" s="82" t="s">
@@ -53245,7 +53287,7 @@
         <v>1085</v>
       </c>
       <c r="F86" s="82" t="str">
-        <f>SUBSTITUTE(E86, "hazr-", "")&amp;"-pb"&amp;H86</f>
+        <f t="shared" si="16"/>
         <v>p-bdp-rlgcap-lb-pb29108</v>
       </c>
       <c r="G86" s="82" t="s">
@@ -53277,7 +53319,7 @@
         <v>1085</v>
       </c>
       <c r="F87" s="82" t="str">
-        <f>SUBSTITUTE(E87, "hazr-", "")&amp;"-pb"&amp;H87</f>
+        <f t="shared" si="16"/>
         <v>p-bdp-rlgcap-lb-pb29109</v>
       </c>
       <c r="G87" s="82" t="s">
